--- a/data/trans_bre/BARTHEL_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Estudios-trans_bre.xlsx
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-4,35</t>
+          <t>4,35</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-9,34</t>
+          <t>9,34</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-9,68</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-9,86</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-4,82%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,38%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-11,51%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-12,38%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -0,19</t>
+          <t>0,36; 8,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,03; -3,99</t>
+          <t>4,04; 14,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -4,09</t>
+          <t>4,56; 15,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -4,89</t>
+          <t>4,82; 14,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; -0,19</t>
+          <t>3,29; 116,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -5,06</t>
+          <t>17,22; 97,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -5,07</t>
+          <t>22,82; 116,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -6,49</t>
+          <t>19,83; 83,15</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>5,98</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-8,55</t>
+          <t>8,55</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-8,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-6,15%</t>
+          <t>215,28%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,18%</t>
+          <t>125,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-8,47%</t>
+          <t>144,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>-23,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 0,92</t>
+          <t>-0,19; 15,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 0,08</t>
+          <t>-0,35; 18,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -1,9</t>
+          <t>1,94; 15,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 10,5</t>
+          <t>-9,2; 4,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 0,94</t>
+          <t>-58,01; 1765,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 0,04</t>
+          <t>-10,34; 493,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -2,04</t>
+          <t>19,89; 420,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 12,15</t>
+          <t>-78,25; 60,21</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-8,97</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-11,19</t>
+          <t>11,19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>-3,47</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-9,3%</t>
+          <t>254,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,62%</t>
+          <t>301,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>-45,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,08%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 3,97</t>
+          <t>-3,51; 25,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 3,4</t>
+          <t>-2,7; 35,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 14,46</t>
+          <t>-13,18; 8,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 3,91</t>
+          <t>-4,17; 7,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 3,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 3,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 17,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 4,23</t>
+          <t>-55,24; 281,08</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-5,52</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,66</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,82</t>
+          <t>9,82</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,12</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-5,99%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,54%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-11,15%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-5,89%</t>
+          <t>39,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -2,15</t>
+          <t>1,99; 8,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -5,68</t>
+          <t>6,12; 15,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -5,71</t>
+          <t>5,8; 14,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 3,19</t>
+          <t>-4,22; 10,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,75; -2,31</t>
+          <t>19,54; 144,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -7,26</t>
+          <t>35,01; 126,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -6,6</t>
+          <t>42,04; 145,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 3,71</t>
+          <t>-29,82; 83,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/BARTHEL_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,86</t>
+          <t>10,57</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 8,3</t>
+          <t>0,29; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 14,82</t>
+          <t>3,17; 14,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 15,59</t>
+          <t>4,38; 15,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 14,23</t>
+          <t>5,72; 15,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 116,04</t>
+          <t>-0,53; 102,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 97,75</t>
+          <t>14,69; 96,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,82; 116,39</t>
+          <t>21,39; 115,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 83,15</t>
+          <t>24,29; 95,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-23,3%</t>
+          <t>54,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 15,6</t>
+          <t>-0,89; 16,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 18,8</t>
+          <t>-0,69; 18,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 15,0</t>
+          <t>2,16; 14,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 4,75</t>
+          <t>0,54; 8,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 1765,38</t>
+          <t>-50,05; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 493,93</t>
+          <t>-14,65; 454,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 420,26</t>
+          <t>24,58; 435,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 60,21</t>
+          <t>3,24; 130,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 25,57</t>
+          <t>-3,41; 25,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 35,71</t>
+          <t>-3,46; 32,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 8,72</t>
+          <t>-15,6; 8,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 7,47</t>
+          <t>-4,13; 6,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,24; 281,08</t>
+          <t>-61,32; 216,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,99</t>
+          <t>2,41; 9,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,7</t>
+          <t>6,01; 15,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 14,13</t>
+          <t>5,79; 13,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 10,64</t>
+          <t>7,47; 13,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 144,47</t>
+          <t>23,43; 143,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,01; 126,1</t>
+          <t>34,81; 126,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,04; 145,9</t>
+          <t>41,47; 135,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 83,67</t>
+          <t>51,51; 119,59</t>
         </is>
       </c>
     </row>
